--- a/Server.Solution/Server.Api/Statement/Extrato-01-JANEIRO-2026.xlsx
+++ b/Server.Solution/Server.Api/Statement/Extrato-01-JANEIRO-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>Data</t>
   </si>
@@ -32,6 +32,15 @@
     <t>Score</t>
   </si>
   <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>IA: Confiança</t>
+  </si>
+  <si>
+    <t>IA: Justificativa</t>
+  </si>
+  <si>
     <t>30-01-2026</t>
   </si>
   <si>
@@ -56,13 +65,64 @@
     <t>02-02-2026</t>
   </si>
   <si>
+    <t>Transferência enviada - 01/02 11:00 RICARDO LAURIS FERNANDES</t>
+  </si>
+  <si>
+    <t>Transferência Pessoal</t>
+  </si>
+  <si>
+    <t>ALTO</t>
+  </si>
+  <si>
+    <t>Usando Serviço de I.A.</t>
+  </si>
+  <si>
+    <t>Transferência para pessoa física sem detalhe da finalidade.</t>
+  </si>
+  <si>
     <t>Transferido da poupança - 02/02 10:46 DIVA LAURIS FERN</t>
   </si>
   <si>
     <t>TRANSFERENCIA</t>
   </si>
   <si>
-    <t>ALTO</t>
+    <t>15-01-2026</t>
+  </si>
+  <si>
+    <t>NuBank</t>
+  </si>
+  <si>
+    <t>Pao de Acucar-2449</t>
+  </si>
+  <si>
+    <t>Supermercado</t>
+  </si>
+  <si>
+    <t>Identificado como rede de supermercados Pão de Açúcar.</t>
+  </si>
+  <si>
+    <t>27-01-2026</t>
+  </si>
+  <si>
+    <t>Organizacao Funeraria</t>
+  </si>
+  <si>
+    <t>Serviços Funerários</t>
+  </si>
+  <si>
+    <t>Identificado como serviço funerário.</t>
+  </si>
+  <si>
+    <t>10-01-2026</t>
+  </si>
+  <si>
+    <t>Chaveiro Carvalho</t>
+  </si>
+  <si>
+    <t>Serviços Domésticos</t>
+  </si>
+  <si>
+    <t>'Chaveiro' indica serviço de chaveiro.</t>
   </si>
   <si>
     <t>Resgate Fundo - BB RF Ref DI Plus Agil</t>
@@ -83,12 +143,21 @@
     <t>Resgate Fundo</t>
   </si>
   <si>
+    <t>19-01-2026</t>
+  </si>
+  <si>
+    <t>Pagamento recebido</t>
+  </si>
+  <si>
+    <t>Receita Não Categorizada</t>
+  </si>
+  <si>
+    <t>Pagamento recebido sem detalhe da origem ou finalidade.</t>
+  </si>
+  <si>
     <t>29-01-2026</t>
   </si>
   <si>
-    <t>NuBank</t>
-  </si>
-  <si>
     <t>Quitanda Guerreiro</t>
   </si>
   <si>
@@ -170,9 +239,6 @@
     <t>17-01-2026</t>
   </si>
   <si>
-    <t>15-01-2026</t>
-  </si>
-  <si>
     <t>13-01-2026</t>
   </si>
   <si>
@@ -182,12 +248,75 @@
     <t>Lanches Alameda Qualit</t>
   </si>
   <si>
-    <t>10-01-2026</t>
-  </si>
-  <si>
     <t>Paladar Pastel</t>
   </si>
   <si>
+    <t>23-01-2026</t>
+  </si>
+  <si>
+    <t>Garagecarservice</t>
+  </si>
+  <si>
+    <t>Manutenção Veicular</t>
+  </si>
+  <si>
+    <t>Nome indica serviço de manutenção e reparo de veículos.</t>
+  </si>
+  <si>
+    <t>Alemao Pneus</t>
+  </si>
+  <si>
+    <t>Nome indica loja especializada em pneus.</t>
+  </si>
+  <si>
+    <t>20-01-2026</t>
+  </si>
+  <si>
+    <t>Simão Mecânica</t>
+  </si>
+  <si>
+    <t>Nome indica oficina mecânica.</t>
+  </si>
+  <si>
+    <t>26-01-2026</t>
+  </si>
+  <si>
+    <t>Festolandia</t>
+  </si>
+  <si>
+    <t>Lazer e Eventos</t>
+  </si>
+  <si>
+    <t>Nome sugere loja de artigos para festas ou eventos.</t>
+  </si>
+  <si>
+    <t>Ouro Pan</t>
+  </si>
+  <si>
+    <t>Joias e Acessórios</t>
+  </si>
+  <si>
+    <t>'Ouro' sugere comércio de joias ou metais preciosos.</t>
+  </si>
+  <si>
+    <t>BB RF Ref DI Plus Ágil</t>
+  </si>
+  <si>
+    <t>Investimentos</t>
+  </si>
+  <si>
+    <t>Identificado como produto de investimento de renda fixa.</t>
+  </si>
+  <si>
+    <t>Aplicação Poupança - 01/02 11:01 FLORA</t>
+  </si>
+  <si>
+    <t>Identificado como aplicação em caderneta de poupança.</t>
+  </si>
+  <si>
+    <t>BB RF LP Selic</t>
+  </si>
+  <si>
     <t>Naturepharma</t>
   </si>
   <si>
@@ -197,13 +326,49 @@
     <t>Farmaciadopovo</t>
   </si>
   <si>
-    <t>26-01-2026</t>
-  </si>
-  <si>
     <t>Drogaria Popular</t>
   </si>
   <si>
-    <t>27-01-2026</t>
+    <t>Andrea Aparecida Devel</t>
+  </si>
+  <si>
+    <t>Despesa Pessoal</t>
+  </si>
+  <si>
+    <t>Nome de pessoa física sem contexto da transação.</t>
+  </si>
+  <si>
+    <t>Luisclaudiosimao</t>
+  </si>
+  <si>
+    <t>Rrfcomerciode</t>
+  </si>
+  <si>
+    <t>Compras Diversas</t>
+  </si>
+  <si>
+    <t>Nome de comerciante genérico e incompleto.</t>
+  </si>
+  <si>
+    <t>12-01-2026</t>
+  </si>
+  <si>
+    <t>Posto Bauru</t>
+  </si>
+  <si>
+    <t>Combustível</t>
+  </si>
+  <si>
+    <t>'Posto' geralmente se refere a posto de combustível.</t>
+  </si>
+  <si>
+    <t>Sandri Material de Contrução</t>
+  </si>
+  <si>
+    <t>Casa e Construção</t>
+  </si>
+  <si>
+    <t>Nome indica loja de materiais de construção.</t>
   </si>
   <si>
     <t>Comacocomercial</t>
@@ -218,15 +383,21 @@
     <t>CASA - ENERGIA</t>
   </si>
   <si>
-    <t>20-01-2026</t>
-  </si>
-  <si>
     <t>Ultraforte</t>
   </si>
   <si>
     <t>CASA - 1,99</t>
   </si>
   <si>
+    <t>Petz Bauru</t>
+  </si>
+  <si>
+    <t>Animais de Estimação</t>
+  </si>
+  <si>
+    <t>Identificado como loja de produtos e serviços para animais de estimação (Petz).</t>
+  </si>
+  <si>
     <t>Pix - Enviado - 02/02 18:42 PIX Marketplace</t>
   </si>
   <si>
@@ -234,72 +405,6 @@
   </si>
   <si>
     <t>Pix - Enviado - 03/02 20:42 PIX Marketplace</t>
-  </si>
-  <si>
-    <t>BB RF Ref DI Plus Ágil</t>
-  </si>
-  <si>
-    <t>Transferência enviada - 01/02 11:00 RICARDO LAURIS FERNANDES</t>
-  </si>
-  <si>
-    <t>Aplicação Poupança - 01/02 11:01 FLORA</t>
-  </si>
-  <si>
-    <t>BB RF LP Selic</t>
-  </si>
-  <si>
-    <t>Andrea Aparecida Devel</t>
-  </si>
-  <si>
-    <t>Petz Bauru</t>
-  </si>
-  <si>
-    <t>Organizacao Funeraria</t>
-  </si>
-  <si>
-    <t>Festolandia</t>
-  </si>
-  <si>
-    <t>23-01-2026</t>
-  </si>
-  <si>
-    <t>Garagecarservice</t>
-  </si>
-  <si>
-    <t>Rrfcomerciode</t>
-  </si>
-  <si>
-    <t>Alemao Pneus</t>
-  </si>
-  <si>
-    <t>Simão Mecânica</t>
-  </si>
-  <si>
-    <t>19-01-2026</t>
-  </si>
-  <si>
-    <t>Pagamento recebido</t>
-  </si>
-  <si>
-    <t>Posto Bauru</t>
-  </si>
-  <si>
-    <t>Sandri Material de Contrução</t>
-  </si>
-  <si>
-    <t>Pao de Acucar-2449</t>
-  </si>
-  <si>
-    <t>12-01-2026</t>
-  </si>
-  <si>
-    <t>Ouro Pan</t>
-  </si>
-  <si>
-    <t>Luisclaudiosimao</t>
-  </si>
-  <si>
-    <t>Chaveiro Carvalho</t>
   </si>
 </sst>
 </file>
@@ -307,7 +412,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -340,6 +445,11 @@
       <color rgb="FFFFA500"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF4500"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -366,14 +476,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" applyFont="1"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0"/>
     <xf numFmtId="0" fontId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="5" applyFont="1"/>
-    <xf numFmtId="4" applyNumberFormat="1" fontId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="6" applyFont="1"/>
+    <xf numFmtId="4" applyNumberFormat="1" fontId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -386,7 +504,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7694673538208" customWidth="1"/>
@@ -395,6 +513,9 @@
     <col min="4" max="4" width="23.163223266601562" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.257373809814453" customWidth="1"/>
+    <col min="8" max="8" width="12.529139518737793" customWidth="1"/>
+    <col min="9" max="9" width="70" customWidth="1" style="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -416,73 +537,93 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I2" s="8"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="E3" s="7">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I3" s="8"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1129.45</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="E4" s="7">
+        <v>281</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>17</v>
@@ -490,1323 +631,1638 @@
       <c r="D5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="5">
-        <v>653.38</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
+      <c r="E5" s="7">
+        <v>1676.64</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1129.45</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="5">
-        <v>56.64</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="I6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5">
-        <v>229.17</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="E7" s="7">
+        <v>34.78</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="5">
-        <v>27</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="E8" s="7">
+        <v>659.5</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="5">
-        <v>3.8</v>
+        <v>35</v>
+      </c>
+      <c r="E9" s="7">
+        <v>35</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="5">
-        <v>5.45</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E10" s="7">
+        <v>653.38</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="8"/>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="5">
-        <v>5.16</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E11" s="7">
+        <v>56.64</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="8"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="5">
-        <v>5.9</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E12" s="7">
+        <v>229.17</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="8"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="5">
-        <v>5.85</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1133.65</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="5">
-        <v>5.02</v>
+        <v>49</v>
+      </c>
+      <c r="E14" s="7">
+        <v>27</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I14" s="8"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="5">
-        <v>5.34</v>
+        <v>52</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.8</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I15" s="8"/>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="5">
-        <v>4.64</v>
+        <v>52</v>
+      </c>
+      <c r="E16" s="7">
+        <v>5.45</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I16" s="8"/>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="5">
-        <v>5.54</v>
+        <v>52</v>
+      </c>
+      <c r="E17" s="7">
+        <v>5.16</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I17" s="8"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="5">
-        <v>62.91</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E18" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="8"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="5">
-        <v>85.29</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E19" s="7">
+        <v>5.85</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="8"/>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="5">
-        <v>75.98</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E20" s="7">
+        <v>5.02</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="8"/>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="5">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="E21" s="7">
+        <v>5.34</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I21" s="8"/>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="5">
-        <v>35.96</v>
+        <v>52</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4.64</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I22" s="8"/>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="5">
-        <v>37.99</v>
+        <v>52</v>
+      </c>
+      <c r="E23" s="7">
+        <v>5.54</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I23" s="8"/>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="5">
-        <v>59.53</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E24" s="7">
+        <v>62.91</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" s="8"/>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="5">
-        <v>5.59</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E25" s="7">
+        <v>85.29</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="5">
-        <v>24</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E26" s="7">
+        <v>75.98</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I26" s="8"/>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B27" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="5">
-        <v>431.3</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="F27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="8"/>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="5">
-        <v>47.24</v>
+        <v>64</v>
+      </c>
+      <c r="E28" s="7">
+        <v>35.96</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I28" s="8"/>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="5">
-        <v>27.3</v>
+        <v>64</v>
+      </c>
+      <c r="E29" s="7">
+        <v>37.99</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I29" s="8"/>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="5">
-        <v>13.8</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E30" s="7">
+        <v>59.53</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="8"/>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="5">
-        <v>9.52</v>
+        <v>64</v>
+      </c>
+      <c r="E31" s="7">
+        <v>5.59</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I31" s="8"/>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B32" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="7">
         <v>24</v>
       </c>
-      <c r="C32" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="5">
-        <v>16.77</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I32" s="8"/>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="5">
-        <v>24</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E33" s="7">
+        <v>431.3</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="8"/>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="5">
-        <v>154.16</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E34" s="7">
+        <v>47.24</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="8"/>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" s="5">
-        <v>84.21</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E35" s="7">
+        <v>27.3</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="8"/>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" s="5">
-        <v>134</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E36" s="7">
+        <v>13.8</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="8"/>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E37" s="5">
-        <v>29.8</v>
+        <v>64</v>
+      </c>
+      <c r="E37" s="7">
+        <v>9.52</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I37" s="8"/>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" s="5">
-        <v>43.75</v>
+        <v>64</v>
+      </c>
+      <c r="E38" s="7">
+        <v>16.77</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I38" s="8"/>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B39" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="7">
         <v>24</v>
       </c>
-      <c r="C39" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="5">
-        <v>88.8</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="F39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="8"/>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="5">
-        <v>75.77</v>
+        <v>64</v>
+      </c>
+      <c r="E40" s="7">
+        <v>154.16</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I40" s="8"/>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="5">
-        <v>84.69</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E41" s="7">
+        <v>84.21</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I41" s="8"/>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="5">
-        <v>139.46</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E42" s="7">
+        <v>134</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I42" s="8"/>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="5">
-        <v>22.15</v>
+        <v>64</v>
+      </c>
+      <c r="E43" s="7">
+        <v>29.8</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I43" s="8"/>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E44" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E44" s="7">
+        <v>43.75</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E45" s="5">
-        <v>220.59</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>16</v>
+        <v>81</v>
+      </c>
+      <c r="E45" s="7">
+        <v>200</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" s="5">
-        <v>32.71</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>10</v>
+        <v>81</v>
+      </c>
+      <c r="E46" s="7">
+        <v>120</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="E47" s="5">
-        <v>4.38</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>10</v>
+        <v>81</v>
+      </c>
+      <c r="E47" s="7">
+        <v>347</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="5">
-        <v>229.17</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>16</v>
+        <v>90</v>
+      </c>
+      <c r="E48" s="7">
+        <v>5.8</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="5">
-        <v>11.98</v>
+        <v>90</v>
+      </c>
+      <c r="E49" s="7">
+        <v>25.9</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="G49" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="5">
-        <v>653.38</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>16</v>
+        <v>93</v>
+      </c>
+      <c r="E50" s="7">
+        <v>5.89</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="7">
+        <v>2800.64</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="5">
-        <v>56.64</v>
-      </c>
-      <c r="F51" s="4" t="s">
+      <c r="G51" s="0" t="s">
         <v>20</v>
+      </c>
+      <c r="H51" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="E52" s="5">
-        <v>2800.64</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>16</v>
+        <v>98</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E52" s="7">
+        <v>281</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="E53" s="5">
-        <v>281</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1691.45</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="5">
-        <v>1676.64</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="7">
+        <v>88.8</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I54" s="8"/>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="5">
-        <v>281</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="7">
+        <v>75.77</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I55" s="8"/>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="5">
-        <v>1691.45</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="7">
+        <v>84.69</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I56" s="8"/>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57" s="5">
-        <v>23.17</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E57" s="7">
+        <v>139.46</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I57" s="8"/>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="E58" s="5">
-        <v>40.97</v>
+        <v>104</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" s="7">
+        <v>22.15</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I58" s="8"/>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="E59" s="5">
-        <v>659.5</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E59" s="7">
+        <v>63.36</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I59" s="8"/>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="5">
-        <v>5.8</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E60" s="7">
+        <v>220.59</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="8"/>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="E61" s="5">
-        <v>200</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="E61" s="7">
+        <v>32.71</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="8"/>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="E62" s="5">
-        <v>13.98</v>
+        <v>105</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E62" s="7">
+        <v>23.17</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="E63" s="5">
-        <v>120</v>
-      </c>
-      <c r="F63" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E63" s="7">
+        <v>22.73</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="0" t="s">
         <v>20</v>
+      </c>
+      <c r="H63" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" s="5">
-        <v>347</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>16</v>
+        <v>108</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64" s="7">
+        <v>188</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="E65" s="5">
-        <v>1133.65</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>16</v>
+        <v>109</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="7">
+        <v>13.98</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="E66" s="5">
-        <v>169.04</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>16</v>
+        <v>109</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="E66" s="7">
+        <v>6.99</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="E67" s="5">
-        <v>24.91</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>10</v>
+        <v>113</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="7">
+        <v>169.04</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="E68" s="5">
-        <v>34.78</v>
+        <v>116</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" s="7">
+        <v>24.91</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="E69" s="5">
-        <v>25.9</v>
+        <v>119</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="E69" s="7">
+        <v>4.38</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I69" s="8"/>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="E70" s="5">
-        <v>6.99</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E70" s="7">
+        <v>229.17</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="8"/>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" s="5">
-        <v>22.73</v>
+        <v>123</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="E71" s="7">
+        <v>11.98</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I71" s="8"/>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="E72" s="5">
-        <v>5.89</v>
+        <v>125</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E72" s="7">
+        <v>40.97</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="G72" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="E73" s="5">
-        <v>188</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="E73" s="7">
+        <v>653.38</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="8"/>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="E74" s="5">
-        <v>35</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="E74" s="7">
+        <v>56.64</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I74" s="8"/>
     </row>
   </sheetData>
   <headerFooter/>
